--- a/data/nzd0065/nzd0065.xlsx
+++ b/data/nzd0065/nzd0065.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC210"/>
+  <dimension ref="A1:AC211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19917,6 +19917,99 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>395.78</v>
+      </c>
+      <c r="C211" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="D211" t="n">
+        <v>373.92</v>
+      </c>
+      <c r="E211" t="n">
+        <v>367.43</v>
+      </c>
+      <c r="F211" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="G211" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="H211" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="I211" t="n">
+        <v>356.78</v>
+      </c>
+      <c r="J211" t="n">
+        <v>354.44</v>
+      </c>
+      <c r="K211" t="n">
+        <v>339.18</v>
+      </c>
+      <c r="L211" t="n">
+        <v>349.11</v>
+      </c>
+      <c r="M211" t="n">
+        <v>350.26</v>
+      </c>
+      <c r="N211" t="n">
+        <v>340.59</v>
+      </c>
+      <c r="O211" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="P211" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>329.31</v>
+      </c>
+      <c r="R211" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="S211" t="n">
+        <v>330.51</v>
+      </c>
+      <c r="T211" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="U211" t="n">
+        <v>330.96</v>
+      </c>
+      <c r="V211" t="n">
+        <v>327.57</v>
+      </c>
+      <c r="W211" t="n">
+        <v>319.01</v>
+      </c>
+      <c r="X211" t="n">
+        <v>332.77</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>341.23</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>331.15</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>304.03</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19928,7 +20021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B213"/>
+  <dimension ref="A1:B214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22061,6 +22154,16 @@
       </c>
       <c r="B213" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -22229,28 +22332,28 @@
         <v>0.0257</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9689121965582355</v>
+        <v>-0.9554822886043028</v>
       </c>
       <c r="J2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1064315230535915</v>
+        <v>0.104493259324097</v>
       </c>
       <c r="M2" t="n">
-        <v>15.55805968518803</v>
+        <v>15.54667670545835</v>
       </c>
       <c r="N2" t="n">
-        <v>473.2041142724183</v>
+        <v>472.0198965770396</v>
       </c>
       <c r="O2" t="n">
-        <v>21.75325525691312</v>
+        <v>21.72601888467005</v>
       </c>
       <c r="P2" t="n">
-        <v>405.8858596289107</v>
+        <v>405.755352992752</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22307,28 +22410,28 @@
         <v>0.0356</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5705974630610138</v>
+        <v>-0.5639703955569959</v>
       </c>
       <c r="J3" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K3" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07968642705892715</v>
+        <v>0.07860492668145203</v>
       </c>
       <c r="M3" t="n">
-        <v>11.47592072721618</v>
+        <v>11.4519006509445</v>
       </c>
       <c r="N3" t="n">
-        <v>227.0502420566563</v>
+        <v>226.2259171851706</v>
       </c>
       <c r="O3" t="n">
-        <v>15.06818642228242</v>
+        <v>15.04080839533469</v>
       </c>
       <c r="P3" t="n">
-        <v>384.0028135083325</v>
+        <v>383.9388175980257</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22385,28 +22488,28 @@
         <v>0.0412</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2220010038138792</v>
+        <v>-0.21740596351887</v>
       </c>
       <c r="J4" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01901810619064015</v>
+        <v>0.01841331212523789</v>
       </c>
       <c r="M4" t="n">
-        <v>9.756405205042569</v>
+        <v>9.732906763182919</v>
       </c>
       <c r="N4" t="n">
-        <v>152.9686582207445</v>
+        <v>152.3635138765552</v>
       </c>
       <c r="O4" t="n">
-        <v>12.36804989562803</v>
+        <v>12.34356163660048</v>
       </c>
       <c r="P4" t="n">
-        <v>374.4913650749056</v>
+        <v>374.4469512918881</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22463,28 +22566,28 @@
         <v>0.0423</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01619416829817443</v>
+        <v>-0.01562874772501241</v>
       </c>
       <c r="J5" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001083481006992626</v>
+        <v>0.0001019024716643058</v>
       </c>
       <c r="M5" t="n">
-        <v>9.887190231116534</v>
+        <v>9.842225733665391</v>
       </c>
       <c r="N5" t="n">
-        <v>145.6289753514869</v>
+        <v>144.9308086905637</v>
       </c>
       <c r="O5" t="n">
-        <v>12.06768309790603</v>
+        <v>12.03872122322648</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2130698229651</v>
+        <v>367.2076046986055</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22541,28 +22644,28 @@
         <v>0.0459</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04485712719528172</v>
+        <v>-0.04635533420017093</v>
       </c>
       <c r="J6" t="n">
+        <v>210</v>
+      </c>
+      <c r="K6" t="n">
         <v>209</v>
       </c>
-      <c r="K6" t="n">
-        <v>208</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0008436993298975848</v>
+        <v>0.0009096032425116585</v>
       </c>
       <c r="M6" t="n">
-        <v>9.729004338348538</v>
+        <v>9.692106215336333</v>
       </c>
       <c r="N6" t="n">
-        <v>143.1557670342565</v>
+        <v>142.4847589436333</v>
       </c>
       <c r="O6" t="n">
-        <v>11.96477191735206</v>
+        <v>11.93669799164046</v>
       </c>
       <c r="P6" t="n">
-        <v>366.0416139275634</v>
+        <v>366.0561313221256</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22619,28 +22722,28 @@
         <v>0.0435</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08975599114946405</v>
+        <v>-0.08955963110299413</v>
       </c>
       <c r="J7" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K7" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004471450829091173</v>
+        <v>0.004494949949228721</v>
       </c>
       <c r="M7" t="n">
-        <v>7.996818703237277</v>
+        <v>7.95970337858954</v>
       </c>
       <c r="N7" t="n">
-        <v>107.276137374061</v>
+        <v>106.7655376672958</v>
       </c>
       <c r="O7" t="n">
-        <v>10.35741943604009</v>
+        <v>10.33274105294891</v>
       </c>
       <c r="P7" t="n">
-        <v>363.6869209160708</v>
+        <v>363.6850124747236</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22697,28 +22800,28 @@
         <v>0.041</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.003687049648433359</v>
+        <v>-0.001964305914911266</v>
       </c>
       <c r="J8" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K8" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L8" t="n">
-        <v>1.031703474163592e-05</v>
+        <v>2.956013573141014e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>7.072160840755346</v>
+        <v>7.049681860576813</v>
       </c>
       <c r="N8" t="n">
-        <v>78.80786674438154</v>
+        <v>78.4509908770596</v>
       </c>
       <c r="O8" t="n">
-        <v>8.877379497598463</v>
+        <v>8.857256396709966</v>
       </c>
       <c r="P8" t="n">
-        <v>359.8810346275393</v>
+        <v>359.8642911227846</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22775,28 +22878,28 @@
         <v>0.0357</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3112349044911309</v>
+        <v>-0.3057152415101731</v>
       </c>
       <c r="J9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04724976932655922</v>
+        <v>0.04601553506810485</v>
       </c>
       <c r="M9" t="n">
-        <v>9.016934658474197</v>
+        <v>9.004657520088411</v>
       </c>
       <c r="N9" t="n">
-        <v>116.822618621793</v>
+        <v>116.4552040321034</v>
       </c>
       <c r="O9" t="n">
-        <v>10.8084512591672</v>
+        <v>10.79144123980219</v>
       </c>
       <c r="P9" t="n">
-        <v>358.5836922174828</v>
+        <v>358.5300461054302</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22853,28 +22956,28 @@
         <v>0.0255</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2669968314544687</v>
+        <v>-0.2550488297141008</v>
       </c>
       <c r="J10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02229586342019396</v>
+        <v>0.02048294980117327</v>
       </c>
       <c r="M10" t="n">
-        <v>10.69898355635948</v>
+        <v>10.71275620912693</v>
       </c>
       <c r="N10" t="n">
-        <v>186.9675969732517</v>
+        <v>186.9623085013608</v>
       </c>
       <c r="O10" t="n">
-        <v>13.67360950785314</v>
+        <v>13.67341612404745</v>
       </c>
       <c r="P10" t="n">
-        <v>347.7000754254445</v>
+        <v>347.5839516978945</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22931,28 +23034,28 @@
         <v>0.0232</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3840431429814126</v>
+        <v>-0.3794809451003577</v>
       </c>
       <c r="J11" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K11" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03582473179642498</v>
+        <v>0.03531704020360604</v>
       </c>
       <c r="M11" t="n">
-        <v>12.29183169059613</v>
+        <v>12.2594306155239</v>
       </c>
       <c r="N11" t="n">
-        <v>237.4127530305234</v>
+        <v>236.4112540308539</v>
       </c>
       <c r="O11" t="n">
-        <v>15.40820408193386</v>
+        <v>15.37567084815664</v>
       </c>
       <c r="P11" t="n">
-        <v>343.9866483193541</v>
+        <v>343.9423078986478</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23009,28 +23112,28 @@
         <v>0.031</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4186164849187854</v>
+        <v>-0.4067206402856693</v>
       </c>
       <c r="J12" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K12" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06629379508010536</v>
+        <v>0.06303067828805897</v>
       </c>
       <c r="M12" t="n">
-        <v>9.862039661058301</v>
+        <v>9.8924412054433</v>
       </c>
       <c r="N12" t="n">
-        <v>147.6185688833785</v>
+        <v>147.7929466549703</v>
       </c>
       <c r="O12" t="n">
-        <v>12.14983822457643</v>
+        <v>12.1570122421165</v>
       </c>
       <c r="P12" t="n">
-        <v>346.3961557892835</v>
+        <v>346.2805389814548</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23087,28 +23190,28 @@
         <v>0.036</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3506334071885202</v>
+        <v>-0.3382473368292505</v>
       </c>
       <c r="J13" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K13" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04549394321342259</v>
+        <v>0.0426121059631388</v>
       </c>
       <c r="M13" t="n">
-        <v>9.720737800482032</v>
+        <v>9.743525640493633</v>
       </c>
       <c r="N13" t="n">
-        <v>154.277525706156</v>
+        <v>154.4939927638193</v>
       </c>
       <c r="O13" t="n">
-        <v>12.4208504421459</v>
+        <v>12.42956124582921</v>
       </c>
       <c r="P13" t="n">
-        <v>345.201370276748</v>
+        <v>345.0809889200098</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23165,28 +23268,28 @@
         <v>0.0414</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3676821464126627</v>
+        <v>-0.3583857328011845</v>
       </c>
       <c r="J14" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K14" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04485265590955223</v>
+        <v>0.04297648702067625</v>
       </c>
       <c r="M14" t="n">
-        <v>10.53580492786502</v>
+        <v>10.53573014514828</v>
       </c>
       <c r="N14" t="n">
-        <v>172.1861701957064</v>
+        <v>171.9020326985382</v>
       </c>
       <c r="O14" t="n">
-        <v>13.12197280121043</v>
+        <v>13.11114154826109</v>
       </c>
       <c r="P14" t="n">
-        <v>339.5305918567674</v>
+        <v>339.4402391580593</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23243,28 +23346,28 @@
         <v>0.042</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3883417112918984</v>
+        <v>-0.3806931556557365</v>
       </c>
       <c r="J15" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K15" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04208223990129334</v>
+        <v>0.04081151150690554</v>
       </c>
       <c r="M15" t="n">
-        <v>11.7105756769216</v>
+        <v>11.68741688380838</v>
       </c>
       <c r="N15" t="n">
-        <v>206.0658364811303</v>
+        <v>205.4368081327421</v>
       </c>
       <c r="O15" t="n">
-        <v>14.35499343368468</v>
+        <v>14.33306694789158</v>
       </c>
       <c r="P15" t="n">
-        <v>336.8673204740724</v>
+        <v>336.7927623509838</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23321,28 +23424,28 @@
         <v>0.0418</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3892999074405</v>
+        <v>-0.3819039601073052</v>
       </c>
       <c r="J16" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K16" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03746061012067259</v>
+        <v>0.03638412524024859</v>
       </c>
       <c r="M16" t="n">
-        <v>12.63615421644437</v>
+        <v>12.60860652828992</v>
       </c>
       <c r="N16" t="n">
-        <v>234.66189089303</v>
+        <v>233.8674628472468</v>
       </c>
       <c r="O16" t="n">
-        <v>15.31867784415581</v>
+        <v>15.2927258148195</v>
       </c>
       <c r="P16" t="n">
-        <v>332.7997434855493</v>
+        <v>332.72774277032</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23399,28 +23502,28 @@
         <v>0.0382</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4945670952481322</v>
+        <v>-0.4936420985693492</v>
       </c>
       <c r="J17" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K17" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1085341864116414</v>
+        <v>0.1091062914067517</v>
       </c>
       <c r="M17" t="n">
-        <v>8.550247631388268</v>
+        <v>8.512681870644235</v>
       </c>
       <c r="N17" t="n">
-        <v>120.0883760413468</v>
+        <v>119.5107019102434</v>
       </c>
       <c r="O17" t="n">
-        <v>10.95848420363632</v>
+        <v>10.93209503755997</v>
       </c>
       <c r="P17" t="n">
-        <v>341.2022753232296</v>
+        <v>341.1932419571587</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23477,28 +23580,28 @@
         <v>0.0385</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7830645496893104</v>
+        <v>-0.7818474141277461</v>
       </c>
       <c r="J18" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K18" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1742764725425401</v>
+        <v>0.1752334389292203</v>
       </c>
       <c r="M18" t="n">
-        <v>9.664389658170013</v>
+        <v>9.623655858021767</v>
       </c>
       <c r="N18" t="n">
-        <v>169.5262985734528</v>
+        <v>168.7081625354043</v>
       </c>
       <c r="O18" t="n">
-        <v>13.02022651774741</v>
+        <v>12.98877063218087</v>
       </c>
       <c r="P18" t="n">
-        <v>341.892243246657</v>
+        <v>341.8801396690192</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -23555,28 +23658,28 @@
         <v>0.0322</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7512066799645337</v>
+        <v>-0.7428545897299017</v>
       </c>
       <c r="J19" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K19" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1341443611535298</v>
+        <v>0.1324613333106509</v>
       </c>
       <c r="M19" t="n">
-        <v>11.15034060994296</v>
+        <v>11.14810042816687</v>
       </c>
       <c r="N19" t="n">
-        <v>214.4420650474824</v>
+        <v>213.8217564033828</v>
       </c>
       <c r="O19" t="n">
-        <v>14.64384051563941</v>
+        <v>14.62264532850957</v>
       </c>
       <c r="P19" t="n">
-        <v>340.7945795848873</v>
+        <v>340.7121554155734</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -23633,28 +23736,28 @@
         <v>0.0311</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7050550648537275</v>
+        <v>-0.7011052366095734</v>
       </c>
       <c r="J20" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K20" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="n">
-        <v>0.136207444578321</v>
+        <v>0.1359706591836339</v>
       </c>
       <c r="M20" t="n">
-        <v>10.92513148562815</v>
+        <v>10.89584185528188</v>
       </c>
       <c r="N20" t="n">
-        <v>187.9136579311034</v>
+        <v>187.1057808863365</v>
       </c>
       <c r="O20" t="n">
-        <v>13.70816026792448</v>
+        <v>13.67866151662276</v>
       </c>
       <c r="P20" t="n">
-        <v>345.0672875821099</v>
+        <v>345.0287807383557</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -23711,28 +23814,28 @@
         <v>0.0339</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5956453573305768</v>
+        <v>-0.5932002747721478</v>
       </c>
       <c r="J21" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K21" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L21" t="n">
-        <v>0.126481834851687</v>
+        <v>0.1266178091350522</v>
       </c>
       <c r="M21" t="n">
-        <v>9.704305922991145</v>
+        <v>9.672797575173179</v>
       </c>
       <c r="N21" t="n">
-        <v>147.2932924272961</v>
+        <v>146.6221661656761</v>
       </c>
       <c r="O21" t="n">
-        <v>12.1364448018065</v>
+        <v>12.10876402304034</v>
       </c>
       <c r="P21" t="n">
-        <v>343.7503919032748</v>
+        <v>343.7267079121993</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -23789,28 +23892,28 @@
         <v>0.038</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6889569780486149</v>
+        <v>-0.6878518043828753</v>
       </c>
       <c r="J22" t="n">
+        <v>210</v>
+      </c>
+      <c r="K22" t="n">
         <v>209</v>
       </c>
-      <c r="K22" t="n">
-        <v>208</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1587923824291204</v>
+        <v>0.159658563521958</v>
       </c>
       <c r="M22" t="n">
-        <v>9.675141262319507</v>
+        <v>9.634870005163842</v>
       </c>
       <c r="N22" t="n">
-        <v>150.6337566946955</v>
+        <v>149.9205405077045</v>
       </c>
       <c r="O22" t="n">
-        <v>12.27329445156008</v>
+        <v>12.24420436401257</v>
       </c>
       <c r="P22" t="n">
-        <v>344.3361457637993</v>
+        <v>344.3254311136521</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -23867,28 +23970,28 @@
         <v>0.052</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7920728652811585</v>
+        <v>-0.7927831478707064</v>
       </c>
       <c r="J23" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K23" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L23" t="n">
-        <v>0.192479501166018</v>
+        <v>0.1942716765248643</v>
       </c>
       <c r="M23" t="n">
-        <v>10.04776092802007</v>
+        <v>10.00320361481703</v>
       </c>
       <c r="N23" t="n">
-        <v>158.3831528357465</v>
+        <v>157.6248197246855</v>
       </c>
       <c r="O23" t="n">
-        <v>12.58503686270909</v>
+        <v>12.55487234999566</v>
       </c>
       <c r="P23" t="n">
-        <v>340.5579078301538</v>
+        <v>340.5647803354446</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -23945,28 +24048,28 @@
         <v>0.0404</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4373647135556438</v>
+        <v>-0.4344669260230291</v>
       </c>
       <c r="J24" t="n">
+        <v>210</v>
+      </c>
+      <c r="K24" t="n">
         <v>209</v>
       </c>
-      <c r="K24" t="n">
-        <v>208</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.0666491524449484</v>
+        <v>0.06640771822555214</v>
       </c>
       <c r="M24" t="n">
-        <v>10.08638168079369</v>
+        <v>10.05439277592651</v>
       </c>
       <c r="N24" t="n">
-        <v>160.4731385166652</v>
+        <v>159.7570208763776</v>
       </c>
       <c r="O24" t="n">
-        <v>12.66779927677516</v>
+        <v>12.63950239828996</v>
       </c>
       <c r="P24" t="n">
-        <v>340.9115293257638</v>
+        <v>340.8834352980326</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24023,28 +24126,28 @@
         <v>0.0364</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1836162176723666</v>
+        <v>-0.1920742248672193</v>
       </c>
       <c r="J25" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K25" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02413984759215648</v>
+        <v>0.02646710041471767</v>
       </c>
       <c r="M25" t="n">
-        <v>6.851635944851979</v>
+        <v>6.872241180850686</v>
       </c>
       <c r="N25" t="n">
-        <v>82.34285198209776</v>
+        <v>82.38826434604204</v>
       </c>
       <c r="O25" t="n">
-        <v>9.074296225167975</v>
+        <v>9.076798132934435</v>
       </c>
       <c r="P25" t="n">
-        <v>355.684363156793</v>
+        <v>355.7659488280316</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24101,28 +24204,28 @@
         <v>0.0501</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4643865850584467</v>
+        <v>-0.4611057744117533</v>
       </c>
       <c r="J26" t="n">
+        <v>210</v>
+      </c>
+      <c r="K26" t="n">
         <v>209</v>
       </c>
-      <c r="K26" t="n">
-        <v>208</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.1316316339625955</v>
+        <v>0.1310350176268597</v>
       </c>
       <c r="M26" t="n">
-        <v>7.45026304879796</v>
+        <v>7.432501462271732</v>
       </c>
       <c r="N26" t="n">
-        <v>85.22512004133274</v>
+        <v>84.88361018891473</v>
       </c>
       <c r="O26" t="n">
-        <v>9.231745232692068</v>
+        <v>9.213230171276235</v>
       </c>
       <c r="P26" t="n">
-        <v>339.5524064523519</v>
+        <v>339.5205990184901</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24179,28 +24282,28 @@
         <v>0.031</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9600817364989142</v>
+        <v>-0.9576234344200744</v>
       </c>
       <c r="J27" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K27" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1531140117437608</v>
+        <v>0.1537074654894901</v>
       </c>
       <c r="M27" t="n">
-        <v>12.90990432253677</v>
+        <v>12.85667612834125</v>
       </c>
       <c r="N27" t="n">
-        <v>304.3800489214847</v>
+        <v>302.9463633575037</v>
       </c>
       <c r="O27" t="n">
-        <v>17.44649102030218</v>
+        <v>17.40535444504086</v>
       </c>
       <c r="P27" t="n">
-        <v>326.380642364799</v>
+        <v>326.3567358539323</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24257,28 +24360,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4909853046287436</v>
+        <v>-0.4779227635113272</v>
       </c>
       <c r="J28" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K28" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0376001441638939</v>
+        <v>0.03593507315722844</v>
       </c>
       <c r="M28" t="n">
-        <v>14.39897599448016</v>
+        <v>14.38980945162171</v>
       </c>
       <c r="N28" t="n">
-        <v>366.4150735743991</v>
+        <v>365.6924842468686</v>
       </c>
       <c r="O28" t="n">
-        <v>19.14197151743778</v>
+        <v>19.12308772784533</v>
       </c>
       <c r="P28" t="n">
-        <v>332.6200746401433</v>
+        <v>332.4924005851312</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24316,7 +24419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC210"/>
+  <dimension ref="A1:AC211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54993,6 +55096,153 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-35.268059972359,173.13710215923376</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>-35.2673867028203,173.136686992484</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>-35.26680859481094,173.1361332372638</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-35.266208602209105,173.13561134661776</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-35.265621398719794,173.13507082568114</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-35.265049762685024,173.13450762841276</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-35.26448848425149,173.1339293418346</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-35.26389721757224,173.1333947210706</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-35.26332122876144,173.13283784568173</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-35.26267044954536,173.13238988073016</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-35.262165477311456,173.13172957367453</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-35.26160967861844,173.13114327866336</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-35.26099124589658,173.1306481911144</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-35.2603992045544,173.13011466445482</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>-35.25981138502734,173.129574983954</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>-35.25923855349303,173.12901347100166</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>-35.25863810809245,173.12849216601938</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>-35.25812054678695,173.12785015250137</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>-35.25756147965001,173.12726857760015</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>-35.256998183200075,173.12669315611095</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>-35.256416071313645,173.1261451296676</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>-35.25580403098027,173.12564068199868</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>-35.25532117796551,173.12494809450146</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>-35.25480764340343,173.12430018224723</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>-35.254186793881644,173.123808546612</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>-35.25346731257249,173.1234605415895</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>-35.253081623804135,173.1226264317487</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0065/nzd0065.xlsx
+++ b/data/nzd0065/nzd0065.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC211"/>
+  <dimension ref="A1:AC212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19906,7 +19906,7 @@
         <v>330.1</v>
       </c>
       <c r="AA210" t="n">
-        <v>304.03</v>
+        <v>308.81</v>
       </c>
       <c r="AB210" t="n">
         <v>332.89</v>
@@ -19924,7 +19924,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>395.78</v>
+        <v>399.57</v>
       </c>
       <c r="C211" t="n">
         <v>376.63</v>
@@ -19999,7 +19999,7 @@
         <v>331.15</v>
       </c>
       <c r="AA211" t="n">
-        <v>304.03</v>
+        <v>308.81</v>
       </c>
       <c r="AB211" t="n">
         <v>334.58</v>
@@ -20007,6 +20007,99 @@
       <c r="AC211" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>402.36</v>
+      </c>
+      <c r="C212" t="n">
+        <v>377.07</v>
+      </c>
+      <c r="D212" t="n">
+        <v>372.4</v>
+      </c>
+      <c r="E212" t="n">
+        <v>365.87</v>
+      </c>
+      <c r="F212" t="n">
+        <v>363.23</v>
+      </c>
+      <c r="G212" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="H212" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="I212" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="J212" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="K212" t="n">
+        <v>341.99</v>
+      </c>
+      <c r="L212" t="n">
+        <v>347.58</v>
+      </c>
+      <c r="M212" t="n">
+        <v>353.81</v>
+      </c>
+      <c r="N212" t="n">
+        <v>344.15</v>
+      </c>
+      <c r="O212" t="n">
+        <v>339.28</v>
+      </c>
+      <c r="P212" t="n">
+        <v>334.38</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>331.8</v>
+      </c>
+      <c r="R212" t="n">
+        <v>322.47</v>
+      </c>
+      <c r="S212" t="n">
+        <v>329.59</v>
+      </c>
+      <c r="T212" t="n">
+        <v>327.03</v>
+      </c>
+      <c r="U212" t="n">
+        <v>328.43</v>
+      </c>
+      <c r="V212" t="n">
+        <v>323.91</v>
+      </c>
+      <c r="W212" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="X212" t="n">
+        <v>330.33</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>345.18</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>330.18</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>314.65</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>335.91</v>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20021,7 +20114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B214"/>
+  <dimension ref="A1:B215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22164,6 +22257,16 @@
       </c>
       <c r="B214" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -22332,28 +22435,28 @@
         <v>0.0257</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9554822886043028</v>
+        <v>-0.9327140489110674</v>
       </c>
       <c r="J2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L2" t="n">
-        <v>0.104493259324097</v>
+        <v>0.1004183031292704</v>
       </c>
       <c r="M2" t="n">
-        <v>15.54667670545835</v>
+        <v>15.57840829260901</v>
       </c>
       <c r="N2" t="n">
-        <v>472.0198965770396</v>
+        <v>472.6266597659009</v>
       </c>
       <c r="O2" t="n">
-        <v>21.72601888467005</v>
+        <v>21.73997837546995</v>
       </c>
       <c r="P2" t="n">
-        <v>405.755352992752</v>
+        <v>405.5313833679802</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22410,28 +22513,28 @@
         <v>0.0356</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5639703955569959</v>
+        <v>-0.5568408438679792</v>
       </c>
       <c r="J3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07860492668145203</v>
+        <v>0.07739920397095257</v>
       </c>
       <c r="M3" t="n">
-        <v>11.4519006509445</v>
+        <v>11.42958575635281</v>
       </c>
       <c r="N3" t="n">
-        <v>226.2259171851706</v>
+        <v>225.4454792819288</v>
       </c>
       <c r="O3" t="n">
-        <v>15.04080839533469</v>
+        <v>15.01484196659854</v>
       </c>
       <c r="P3" t="n">
-        <v>383.9388175980257</v>
+        <v>383.8689773180472</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22488,28 +22591,28 @@
         <v>0.0412</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.21740596351887</v>
+        <v>-0.2141213155479199</v>
       </c>
       <c r="J4" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K4" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01841331212523789</v>
+        <v>0.018040926107591</v>
       </c>
       <c r="M4" t="n">
-        <v>9.732906763182919</v>
+        <v>9.702533933164691</v>
       </c>
       <c r="N4" t="n">
-        <v>152.3635138765552</v>
+        <v>151.6993396885929</v>
       </c>
       <c r="O4" t="n">
-        <v>12.34356163660048</v>
+        <v>12.31662858450286</v>
       </c>
       <c r="P4" t="n">
-        <v>374.4469512918881</v>
+        <v>374.4147494053719</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22566,28 +22669,28 @@
         <v>0.0423</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01562874772501241</v>
+        <v>-0.0164442391054904</v>
       </c>
       <c r="J5" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K5" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001019024716643058</v>
+        <v>0.0001139508585235038</v>
       </c>
       <c r="M5" t="n">
-        <v>9.842225733665391</v>
+        <v>9.800240121789447</v>
       </c>
       <c r="N5" t="n">
-        <v>144.9308086905637</v>
+        <v>144.241356435426</v>
       </c>
       <c r="O5" t="n">
-        <v>12.03872122322648</v>
+        <v>12.01005230777227</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2076046986055</v>
+        <v>367.2155995769369</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22644,28 +22747,28 @@
         <v>0.0459</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04635533420017093</v>
+        <v>-0.04776112362328169</v>
       </c>
       <c r="J6" t="n">
+        <v>211</v>
+      </c>
+      <c r="K6" t="n">
         <v>210</v>
       </c>
-      <c r="K6" t="n">
-        <v>209</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0009096032425116585</v>
+        <v>0.0009751489183577045</v>
       </c>
       <c r="M6" t="n">
-        <v>9.692106215336333</v>
+        <v>9.654758989075145</v>
       </c>
       <c r="N6" t="n">
-        <v>142.4847589436333</v>
+        <v>141.8182165611647</v>
       </c>
       <c r="O6" t="n">
-        <v>11.93669799164046</v>
+        <v>11.90874538149022</v>
       </c>
       <c r="P6" t="n">
-        <v>366.0561313221256</v>
+        <v>366.0699481602434</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22722,28 +22825,28 @@
         <v>0.0435</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08955963110299413</v>
+        <v>-0.08942069949785859</v>
       </c>
       <c r="J7" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K7" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004494949949228721</v>
+        <v>0.004525724222118499</v>
       </c>
       <c r="M7" t="n">
-        <v>7.95970337858954</v>
+        <v>7.92265288220549</v>
       </c>
       <c r="N7" t="n">
-        <v>106.7655376672958</v>
+        <v>106.259656358563</v>
       </c>
       <c r="O7" t="n">
-        <v>10.33274105294891</v>
+        <v>10.30823245559407</v>
       </c>
       <c r="P7" t="n">
-        <v>363.6850124747236</v>
+        <v>363.6836429701498</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22800,28 +22903,28 @@
         <v>0.041</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001964305914911266</v>
+        <v>0.0002107502316116236</v>
       </c>
       <c r="J8" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K8" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L8" t="n">
-        <v>2.956013573141014e-06</v>
+        <v>3.435519058125891e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.049681860576813</v>
+        <v>7.030025571753585</v>
       </c>
       <c r="N8" t="n">
-        <v>78.4509908770596</v>
+        <v>78.10773911761451</v>
       </c>
       <c r="O8" t="n">
-        <v>8.857256396709966</v>
+        <v>8.837858287934612</v>
       </c>
       <c r="P8" t="n">
-        <v>359.8642911227846</v>
+        <v>359.8428507216733</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22878,28 +22981,28 @@
         <v>0.0357</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3057152415101731</v>
+        <v>-0.3006643083997436</v>
       </c>
       <c r="J9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04601553506810485</v>
+        <v>0.04494388766724122</v>
       </c>
       <c r="M9" t="n">
-        <v>9.004657520088411</v>
+        <v>8.989210109966418</v>
       </c>
       <c r="N9" t="n">
-        <v>116.4552040321034</v>
+        <v>116.057264758988</v>
       </c>
       <c r="O9" t="n">
-        <v>10.79144123980219</v>
+        <v>10.77298773595273</v>
       </c>
       <c r="P9" t="n">
-        <v>358.5300461054302</v>
+        <v>358.4802570312278</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22956,28 +23059,28 @@
         <v>0.0255</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2550488297141008</v>
+        <v>-0.2416203753068205</v>
       </c>
       <c r="J10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02048294980117327</v>
+        <v>0.01849633359373626</v>
       </c>
       <c r="M10" t="n">
-        <v>10.71275620912693</v>
+        <v>10.73249597044835</v>
       </c>
       <c r="N10" t="n">
-        <v>186.9623085013608</v>
+        <v>187.1646005832864</v>
       </c>
       <c r="O10" t="n">
-        <v>13.67341612404745</v>
+        <v>13.68081140076445</v>
       </c>
       <c r="P10" t="n">
-        <v>347.5839516978945</v>
+        <v>347.4515820350441</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23034,28 +23137,28 @@
         <v>0.0232</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3794809451003577</v>
+        <v>-0.3723618668531823</v>
       </c>
       <c r="J11" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K11" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03531704020360604</v>
+        <v>0.0343350710338538</v>
       </c>
       <c r="M11" t="n">
-        <v>12.2594306155239</v>
+        <v>12.24154630953535</v>
       </c>
       <c r="N11" t="n">
-        <v>236.4112540308539</v>
+        <v>235.5967161308814</v>
       </c>
       <c r="O11" t="n">
-        <v>15.37567084815664</v>
+        <v>15.34916011157879</v>
       </c>
       <c r="P11" t="n">
-        <v>343.9423078986478</v>
+        <v>343.8721322880522</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23112,28 +23215,28 @@
         <v>0.031</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4067206402856693</v>
+        <v>-0.3961130844050086</v>
       </c>
       <c r="J12" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K12" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06303067828805897</v>
+        <v>0.06028297886834932</v>
       </c>
       <c r="M12" t="n">
-        <v>9.8924412054433</v>
+        <v>9.912778831783669</v>
       </c>
       <c r="N12" t="n">
-        <v>147.7929466549703</v>
+        <v>147.7716392699215</v>
       </c>
       <c r="O12" t="n">
-        <v>12.1570122421165</v>
+        <v>12.15613586917823</v>
       </c>
       <c r="P12" t="n">
-        <v>346.2805389814548</v>
+        <v>346.1759760471808</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23190,28 +23293,28 @@
         <v>0.036</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3382473368292505</v>
+        <v>-0.3226995983373241</v>
       </c>
       <c r="J13" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K13" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0426121059631388</v>
+        <v>0.03895308275933629</v>
       </c>
       <c r="M13" t="n">
-        <v>9.743525640493633</v>
+        <v>9.785386531800357</v>
       </c>
       <c r="N13" t="n">
-        <v>154.4939927638193</v>
+        <v>155.2208052256273</v>
       </c>
       <c r="O13" t="n">
-        <v>12.42956124582921</v>
+        <v>12.45876419335511</v>
       </c>
       <c r="P13" t="n">
-        <v>345.0809889200098</v>
+        <v>344.927728623639</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23268,28 +23371,28 @@
         <v>0.0414</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3583857328011845</v>
+        <v>-0.3459053532155055</v>
       </c>
       <c r="J14" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K14" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04297648702067625</v>
+        <v>0.04032651146342381</v>
       </c>
       <c r="M14" t="n">
-        <v>10.53573014514828</v>
+        <v>10.55113215812219</v>
       </c>
       <c r="N14" t="n">
-        <v>171.9020326985382</v>
+        <v>172.0274436563664</v>
       </c>
       <c r="O14" t="n">
-        <v>13.11114154826109</v>
+        <v>13.11592328646239</v>
       </c>
       <c r="P14" t="n">
-        <v>339.4402391580593</v>
+        <v>339.3172150491116</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23346,28 +23449,28 @@
         <v>0.042</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3806931556557365</v>
+        <v>-0.3696238851215012</v>
       </c>
       <c r="J15" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K15" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04081151150690554</v>
+        <v>0.03879526644643283</v>
       </c>
       <c r="M15" t="n">
-        <v>11.68741688380838</v>
+        <v>11.67792470105582</v>
       </c>
       <c r="N15" t="n">
-        <v>205.4368081327421</v>
+        <v>205.1959883296413</v>
       </c>
       <c r="O15" t="n">
-        <v>14.33306694789158</v>
+        <v>14.32466363757423</v>
       </c>
       <c r="P15" t="n">
-        <v>336.7927623509838</v>
+        <v>336.6832955858426</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23424,28 +23527,28 @@
         <v>0.0418</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3819039601073052</v>
+        <v>-0.3715480789077861</v>
       </c>
       <c r="J16" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K16" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03638412524024859</v>
+        <v>0.03474060012477898</v>
       </c>
       <c r="M16" t="n">
-        <v>12.60860652828992</v>
+        <v>12.59343192806715</v>
       </c>
       <c r="N16" t="n">
-        <v>233.8674628472468</v>
+        <v>233.3952165342882</v>
       </c>
       <c r="O16" t="n">
-        <v>15.2927258148195</v>
+        <v>15.27727778546585</v>
       </c>
       <c r="P16" t="n">
-        <v>332.72774277032</v>
+        <v>332.625453674029</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23502,28 +23605,28 @@
         <v>0.0382</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4936420985693492</v>
+        <v>-0.4903767442948465</v>
       </c>
       <c r="J17" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K17" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1091062914067517</v>
+        <v>0.1087366213052365</v>
       </c>
       <c r="M17" t="n">
-        <v>8.512681870644235</v>
+        <v>8.485072921906593</v>
       </c>
       <c r="N17" t="n">
-        <v>119.5107019102434</v>
+        <v>118.9973881203273</v>
       </c>
       <c r="O17" t="n">
-        <v>10.93209503755997</v>
+        <v>10.90859239867029</v>
       </c>
       <c r="P17" t="n">
-        <v>341.1932419571587</v>
+        <v>341.1608945834615</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23580,28 +23683,28 @@
         <v>0.0385</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7818474141277461</v>
+        <v>-0.7806914862043306</v>
       </c>
       <c r="J18" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K18" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1752334389292203</v>
+        <v>0.1762642359281051</v>
       </c>
       <c r="M18" t="n">
-        <v>9.623655858021767</v>
+        <v>9.582841823456977</v>
       </c>
       <c r="N18" t="n">
-        <v>168.7081625354043</v>
+        <v>167.8969336879563</v>
       </c>
       <c r="O18" t="n">
-        <v>12.98877063218087</v>
+        <v>12.95750491753549</v>
       </c>
       <c r="P18" t="n">
-        <v>341.8801396690192</v>
+        <v>341.8684835518148</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -23658,28 +23761,28 @@
         <v>0.0322</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7428545897299017</v>
+        <v>-0.7351673893351058</v>
       </c>
       <c r="J19" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K19" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1324613333106509</v>
+        <v>0.1310484280178374</v>
       </c>
       <c r="M19" t="n">
-        <v>11.14810042816687</v>
+        <v>11.14130474787893</v>
       </c>
       <c r="N19" t="n">
-        <v>213.8217564033828</v>
+        <v>213.1356426349748</v>
       </c>
       <c r="O19" t="n">
-        <v>14.62264532850957</v>
+        <v>14.59916581983282</v>
       </c>
       <c r="P19" t="n">
-        <v>340.7121554155734</v>
+        <v>340.6352219063874</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -23736,28 +23839,28 @@
         <v>0.0311</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7011052366095734</v>
+        <v>-0.7006149140939604</v>
       </c>
       <c r="J20" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K20" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1359706591836339</v>
+        <v>0.1369889231263259</v>
       </c>
       <c r="M20" t="n">
-        <v>10.89584185528188</v>
+        <v>10.84650968730926</v>
       </c>
       <c r="N20" t="n">
-        <v>187.1057808863365</v>
+        <v>186.211971619486</v>
       </c>
       <c r="O20" t="n">
-        <v>13.67866151662276</v>
+        <v>13.64595074076871</v>
       </c>
       <c r="P20" t="n">
-        <v>345.0287807383557</v>
+        <v>345.023932715189</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -23814,28 +23917,28 @@
         <v>0.0339</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5932002747721478</v>
+        <v>-0.5928443192402878</v>
       </c>
       <c r="J21" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K21" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1266178091350522</v>
+        <v>0.1275959535559601</v>
       </c>
       <c r="M21" t="n">
-        <v>9.672797575173179</v>
+        <v>9.62866116406413</v>
       </c>
       <c r="N21" t="n">
-        <v>146.6221661656761</v>
+        <v>145.9213885814862</v>
       </c>
       <c r="O21" t="n">
-        <v>12.10876402304034</v>
+        <v>12.07979257195612</v>
       </c>
       <c r="P21" t="n">
-        <v>343.7267079121993</v>
+        <v>343.7232105985029</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -23892,28 +23995,28 @@
         <v>0.038</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6878518043828753</v>
+        <v>-0.6898084615231764</v>
       </c>
       <c r="J22" t="n">
+        <v>211</v>
+      </c>
+      <c r="K22" t="n">
         <v>210</v>
       </c>
-      <c r="K22" t="n">
-        <v>209</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.159658563521958</v>
+        <v>0.1617587595907578</v>
       </c>
       <c r="M22" t="n">
-        <v>9.634870005163842</v>
+        <v>9.599376758765898</v>
       </c>
       <c r="N22" t="n">
-        <v>149.9205405077045</v>
+        <v>149.2295869464966</v>
       </c>
       <c r="O22" t="n">
-        <v>12.24420436401257</v>
+        <v>12.21595624363875</v>
       </c>
       <c r="P22" t="n">
-        <v>344.3254311136521</v>
+        <v>344.3446705103065</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -23970,28 +24073,28 @@
         <v>0.052</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7927831478707064</v>
+        <v>-0.7957829097248427</v>
       </c>
       <c r="J23" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K23" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1942716765248643</v>
+        <v>0.1969839341786889</v>
       </c>
       <c r="M23" t="n">
-        <v>10.00320361481703</v>
+        <v>9.970683377788221</v>
       </c>
       <c r="N23" t="n">
-        <v>157.6248197246855</v>
+        <v>156.9249022697199</v>
       </c>
       <c r="O23" t="n">
-        <v>12.55487234999566</v>
+        <v>12.52696700202087</v>
       </c>
       <c r="P23" t="n">
-        <v>340.5647803354446</v>
+        <v>340.5942211853903</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24048,28 +24151,28 @@
         <v>0.0404</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4344669260230291</v>
+        <v>-0.4336314419746095</v>
       </c>
       <c r="J24" t="n">
+        <v>211</v>
+      </c>
+      <c r="K24" t="n">
         <v>210</v>
       </c>
-      <c r="K24" t="n">
-        <v>209</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.06640771822555214</v>
+        <v>0.06679111664642234</v>
       </c>
       <c r="M24" t="n">
-        <v>10.05439277592651</v>
+        <v>10.01107732586755</v>
       </c>
       <c r="N24" t="n">
-        <v>159.7570208763776</v>
+        <v>159.0004582110158</v>
       </c>
       <c r="O24" t="n">
-        <v>12.63950239828996</v>
+        <v>12.60953838215404</v>
       </c>
       <c r="P24" t="n">
-        <v>340.8834352980326</v>
+        <v>340.8752201597363</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24126,28 +24229,28 @@
         <v>0.0364</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1920742248672193</v>
+        <v>-0.1969551005154991</v>
       </c>
       <c r="J25" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K25" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02646710041471767</v>
+        <v>0.02801693403909333</v>
       </c>
       <c r="M25" t="n">
-        <v>6.872241180850686</v>
+        <v>6.869294813735237</v>
       </c>
       <c r="N25" t="n">
-        <v>82.38826434604204</v>
+        <v>82.13591711510473</v>
       </c>
       <c r="O25" t="n">
-        <v>9.076798132934435</v>
+        <v>9.062886798096109</v>
       </c>
       <c r="P25" t="n">
-        <v>355.7659488280316</v>
+        <v>355.8137072607071</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24204,28 +24307,28 @@
         <v>0.0501</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4611057744117533</v>
+        <v>-0.4585775586157871</v>
       </c>
       <c r="J26" t="n">
+        <v>211</v>
+      </c>
+      <c r="K26" t="n">
         <v>210</v>
       </c>
-      <c r="K26" t="n">
-        <v>209</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.1310350176268597</v>
+        <v>0.1308750083165576</v>
       </c>
       <c r="M26" t="n">
-        <v>7.432501462271732</v>
+        <v>7.410457452111666</v>
       </c>
       <c r="N26" t="n">
-        <v>84.88361018891473</v>
+        <v>84.5177249415226</v>
       </c>
       <c r="O26" t="n">
-        <v>9.213230171276235</v>
+        <v>9.193352214590856</v>
       </c>
       <c r="P26" t="n">
-        <v>339.5205990184901</v>
+        <v>339.4957396062177</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24282,28 +24385,28 @@
         <v>0.031</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9576234344200744</v>
+        <v>-0.9371212374814949</v>
       </c>
       <c r="J27" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K27" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1537074654894901</v>
+        <v>0.1488880303594421</v>
       </c>
       <c r="M27" t="n">
-        <v>12.85667612834125</v>
+        <v>12.86942256814257</v>
       </c>
       <c r="N27" t="n">
-        <v>302.9463633575037</v>
+        <v>302.8145541006371</v>
       </c>
       <c r="O27" t="n">
-        <v>17.40535444504086</v>
+        <v>17.40156757595813</v>
       </c>
       <c r="P27" t="n">
-        <v>326.3567358539323</v>
+        <v>326.1558301478897</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24360,28 +24463,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4779227635113272</v>
+        <v>-0.4635968077576765</v>
       </c>
       <c r="J28" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K28" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L28" t="n">
-        <v>0.03593507315722844</v>
+        <v>0.03410594321844318</v>
       </c>
       <c r="M28" t="n">
-        <v>14.38980945162171</v>
+        <v>14.38598657268025</v>
       </c>
       <c r="N28" t="n">
-        <v>365.6924842468686</v>
+        <v>365.1595587799602</v>
       </c>
       <c r="O28" t="n">
-        <v>19.12308772784533</v>
+        <v>19.10914856240225</v>
       </c>
       <c r="P28" t="n">
-        <v>332.4924005851312</v>
+        <v>332.3503988709059</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24419,7 +24522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC211"/>
+  <dimension ref="A1:AC212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55082,7 +55185,7 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>-35.25346731257249,173.1234605415895</t>
+          <t>-35.25349497945973,173.1234202506661</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
@@ -55104,7 +55207,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>-35.268059972359,173.13710215923376</t>
+          <t>-35.26808191129519,173.13707020969716</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -55229,7 +55332,7 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>-35.25346731257249,173.1234605415895</t>
+          <t>-35.25349497945973,173.1234202506661</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
@@ -55240,6 +55343,153 @@
       <c r="AC211" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>-35.26809806158843,173.13704669010647</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>-35.26738924981496,173.13668328332773</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>-35.26679979613772,173.13614605065825</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-35.26619957202576,173.1356244971457</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-35.26562186180424,173.13507015129795</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-35.26504924171725,173.1345083870909</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-35.264491552159136,173.1339248740798</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-35.26389374448262,173.1333997788834</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-35.26333083760144,173.13282385245412</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-35.26268671506432,173.1323661935367</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-35.26215662104302,173.1317424709383</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>-35.26163022737801,173.13111335373517</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>-35.2610118524692,173.13061818204355</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-35.26042120024814,173.13008263244245</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>-35.2598303707091,173.12954733539073</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>-35.25925296634337,173.12899248178064</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>-35.258636487376165,173.12849452624164</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>-35.25811522160391,173.12785790749666</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>-35.257537921605035,173.12730288489254</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>-35.25698353907563,173.12671448218822</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>-35.25639488661791,173.1261759806987</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>-35.25578776628592,173.12566436805727</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>-35.25530705496824,173.12496866171946</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>-35.25483050632409,173.1242668870245</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>-35.25418117946054,173.12381672286222</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>-35.253528781663505,173.1233710248982</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>-35.25308932185628,173.12261522109003</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0065/nzd0065.xlsx
+++ b/data/nzd0065/nzd0065.xlsx
@@ -20114,7 +20114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B215"/>
+  <dimension ref="A1:B216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22267,6 +22267,16 @@
       </c>
       <c r="B215" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0065/nzd0065.xlsx
+++ b/data/nzd0065/nzd0065.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC212"/>
+  <dimension ref="A1:AC214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20103,6 +20103,192 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>412.33</v>
+      </c>
+      <c r="C213" t="n">
+        <v>389.6</v>
+      </c>
+      <c r="D213" t="n">
+        <v>380.31</v>
+      </c>
+      <c r="E213" t="n">
+        <v>370.66</v>
+      </c>
+      <c r="F213" t="n">
+        <v>365.38</v>
+      </c>
+      <c r="G213" t="n">
+        <v>363.75</v>
+      </c>
+      <c r="H213" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="I213" t="n">
+        <v>367.99</v>
+      </c>
+      <c r="J213" t="n">
+        <v>370.85</v>
+      </c>
+      <c r="K213" t="n">
+        <v>359.14</v>
+      </c>
+      <c r="L213" t="n">
+        <v>362.05</v>
+      </c>
+      <c r="M213" t="n">
+        <v>362.26</v>
+      </c>
+      <c r="N213" t="n">
+        <v>350.83</v>
+      </c>
+      <c r="O213" t="n">
+        <v>344.13</v>
+      </c>
+      <c r="P213" t="n">
+        <v>343.39</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>342.05</v>
+      </c>
+      <c r="R213" t="n">
+        <v>334.42</v>
+      </c>
+      <c r="S213" t="n">
+        <v>343.84</v>
+      </c>
+      <c r="T213" t="n">
+        <v>340.72</v>
+      </c>
+      <c r="U213" t="n">
+        <v>338.19</v>
+      </c>
+      <c r="V213" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="W213" t="n">
+        <v>325.94</v>
+      </c>
+      <c r="X213" t="n">
+        <v>343.07</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>350.54</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>342.85</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>345.96</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>427.06</v>
+      </c>
+      <c r="C214" t="n">
+        <v>396.23</v>
+      </c>
+      <c r="D214" t="n">
+        <v>385.77</v>
+      </c>
+      <c r="E214" t="n">
+        <v>378.46</v>
+      </c>
+      <c r="F214" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="G214" t="n">
+        <v>370.27</v>
+      </c>
+      <c r="H214" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="I214" t="n">
+        <v>367.68</v>
+      </c>
+      <c r="J214" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="K214" t="n">
+        <v>369.77</v>
+      </c>
+      <c r="L214" t="n">
+        <v>360.04</v>
+      </c>
+      <c r="M214" t="n">
+        <v>358.93</v>
+      </c>
+      <c r="N214" t="n">
+        <v>351.16</v>
+      </c>
+      <c r="O214" t="n">
+        <v>349.88</v>
+      </c>
+      <c r="P214" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>345.55</v>
+      </c>
+      <c r="R214" t="n">
+        <v>339.58</v>
+      </c>
+      <c r="S214" t="n">
+        <v>343.96</v>
+      </c>
+      <c r="T214" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="U214" t="n">
+        <v>345.73</v>
+      </c>
+      <c r="V214" t="n">
+        <v>343.87</v>
+      </c>
+      <c r="W214" t="n">
+        <v>336.85</v>
+      </c>
+      <c r="X214" t="n">
+        <v>344.89</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>351.19</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>346.8</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>344.12</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>350.28</v>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20114,7 +20300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B216"/>
+  <dimension ref="A1:B218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22277,6 +22463,26 @@
       </c>
       <c r="B216" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22445,28 +22651,28 @@
         <v>0.0257</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9327140489110674</v>
+        <v>-0.8645591598677195</v>
       </c>
       <c r="J2" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K2" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1004183031292704</v>
+        <v>0.08665800889308239</v>
       </c>
       <c r="M2" t="n">
-        <v>15.57840829260901</v>
+        <v>15.76291437192226</v>
       </c>
       <c r="N2" t="n">
-        <v>472.6266597659009</v>
+        <v>482.7285445734694</v>
       </c>
       <c r="O2" t="n">
-        <v>21.73997837546995</v>
+        <v>21.97108428306326</v>
       </c>
       <c r="P2" t="n">
-        <v>405.5313833679802</v>
+        <v>404.8551138534483</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22523,28 +22729,28 @@
         <v>0.0356</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5568408438679792</v>
+        <v>-0.5153402435936807</v>
       </c>
       <c r="J3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07739920397095257</v>
+        <v>0.06680014255271405</v>
       </c>
       <c r="M3" t="n">
-        <v>11.42958575635281</v>
+        <v>11.5084846840155</v>
       </c>
       <c r="N3" t="n">
-        <v>225.4454792819288</v>
+        <v>228.6656385830702</v>
       </c>
       <c r="O3" t="n">
-        <v>15.01484196659854</v>
+        <v>15.12169430265902</v>
       </c>
       <c r="P3" t="n">
-        <v>383.8689773180472</v>
+        <v>383.4597742194393</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22601,28 +22807,28 @@
         <v>0.0412</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2141213155479199</v>
+        <v>-0.1891989893279764</v>
       </c>
       <c r="J4" t="n">
+        <v>213</v>
+      </c>
+      <c r="K4" t="n">
         <v>211</v>
       </c>
-      <c r="K4" t="n">
-        <v>209</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.018040926107591</v>
+        <v>0.01424034838416122</v>
       </c>
       <c r="M4" t="n">
-        <v>9.702533933164691</v>
+        <v>9.730856488220079</v>
       </c>
       <c r="N4" t="n">
-        <v>151.6993396885929</v>
+        <v>152.219247989604</v>
       </c>
       <c r="O4" t="n">
-        <v>12.31662858450286</v>
+        <v>12.33771648197526</v>
       </c>
       <c r="P4" t="n">
-        <v>374.4147494053719</v>
+        <v>374.1688123512546</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22679,28 +22885,28 @@
         <v>0.0423</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0164442391054904</v>
+        <v>-0.002893991096157725</v>
       </c>
       <c r="J5" t="n">
+        <v>213</v>
+      </c>
+      <c r="K5" t="n">
         <v>211</v>
       </c>
-      <c r="K5" t="n">
-        <v>209</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0001139508585235038</v>
+        <v>3.583394073247703e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>9.800240121789447</v>
+        <v>9.767900641636455</v>
       </c>
       <c r="N5" t="n">
-        <v>144.241356435426</v>
+        <v>143.575315057384</v>
       </c>
       <c r="O5" t="n">
-        <v>12.01005230777227</v>
+        <v>11.98229172810377</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2155995769369</v>
+        <v>367.0818394169555</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22757,28 +22963,28 @@
         <v>0.0459</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04776112362328169</v>
+        <v>-0.03910265227984999</v>
       </c>
       <c r="J6" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K6" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009751489183577045</v>
+        <v>0.0006649876109268149</v>
       </c>
       <c r="M6" t="n">
-        <v>9.654758989075145</v>
+        <v>9.602130031175367</v>
       </c>
       <c r="N6" t="n">
-        <v>141.8182165611647</v>
+        <v>140.8928470236337</v>
       </c>
       <c r="O6" t="n">
-        <v>11.90874538149022</v>
+        <v>11.86982927525218</v>
       </c>
       <c r="P6" t="n">
-        <v>366.0699481602434</v>
+        <v>365.9842251332005</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22835,28 +23041,28 @@
         <v>0.0435</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08942069949785859</v>
+        <v>-0.07954969555132714</v>
       </c>
       <c r="J7" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K7" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004525724222118499</v>
+        <v>0.003642857368297836</v>
       </c>
       <c r="M7" t="n">
-        <v>7.92265288220549</v>
+        <v>7.895590109437227</v>
       </c>
       <c r="N7" t="n">
-        <v>106.259656358563</v>
+        <v>105.6585105760551</v>
       </c>
       <c r="O7" t="n">
-        <v>10.30823245559407</v>
+        <v>10.27903257004545</v>
       </c>
       <c r="P7" t="n">
-        <v>363.6836429701498</v>
+        <v>363.5856647605222</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22913,28 +23119,28 @@
         <v>0.041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002107502316116236</v>
+        <v>0.01732743057497598</v>
       </c>
       <c r="J8" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K8" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L8" t="n">
-        <v>3.435519058125891e-08</v>
+        <v>0.000234052207219837</v>
       </c>
       <c r="M8" t="n">
-        <v>7.030025571753585</v>
+        <v>7.072036368093356</v>
       </c>
       <c r="N8" t="n">
-        <v>78.10773911761451</v>
+        <v>78.29039851545312</v>
       </c>
       <c r="O8" t="n">
-        <v>8.837858287934612</v>
+        <v>8.848186170930918</v>
       </c>
       <c r="P8" t="n">
-        <v>359.8428507216733</v>
+        <v>359.6730281301284</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22991,28 +23197,28 @@
         <v>0.0357</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3006643083997436</v>
+        <v>-0.2706789903082319</v>
       </c>
       <c r="J9" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K9" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04494388766724122</v>
+        <v>0.03660561549284957</v>
       </c>
       <c r="M9" t="n">
-        <v>8.989210109966418</v>
+        <v>9.064239883532577</v>
       </c>
       <c r="N9" t="n">
-        <v>116.057264758988</v>
+        <v>117.7118165786675</v>
       </c>
       <c r="O9" t="n">
-        <v>10.77298773595273</v>
+        <v>10.84950766526608</v>
       </c>
       <c r="P9" t="n">
-        <v>358.4802570312278</v>
+        <v>358.1828110375238</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23069,28 +23275,28 @@
         <v>0.0255</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2416203753068205</v>
+        <v>-0.1902652096535137</v>
       </c>
       <c r="J10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01849633359373626</v>
+        <v>0.01129425734119494</v>
       </c>
       <c r="M10" t="n">
-        <v>10.73249597044835</v>
+        <v>10.89902886001075</v>
       </c>
       <c r="N10" t="n">
-        <v>187.1646005832864</v>
+        <v>193.4562277252201</v>
       </c>
       <c r="O10" t="n">
-        <v>13.68081140076445</v>
+        <v>13.90885429232832</v>
       </c>
       <c r="P10" t="n">
-        <v>347.4515820350441</v>
+        <v>346.9421503218221</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23147,28 +23353,28 @@
         <v>0.0232</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3723618668531823</v>
+        <v>-0.3196494181922851</v>
       </c>
       <c r="J11" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K11" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0343350710338538</v>
+        <v>0.0251141042250278</v>
       </c>
       <c r="M11" t="n">
-        <v>12.24154630953535</v>
+        <v>12.42809760917491</v>
       </c>
       <c r="N11" t="n">
-        <v>235.5967161308814</v>
+        <v>242.1243684592201</v>
       </c>
       <c r="O11" t="n">
-        <v>15.34916011157879</v>
+        <v>15.56034602633309</v>
       </c>
       <c r="P11" t="n">
-        <v>343.8721322880522</v>
+        <v>343.3491372736301</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23225,28 +23431,28 @@
         <v>0.031</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3961130844050086</v>
+        <v>-0.3522028456352844</v>
       </c>
       <c r="J12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06028297886834932</v>
+        <v>0.04737229724855452</v>
       </c>
       <c r="M12" t="n">
-        <v>9.912778831783669</v>
+        <v>10.0925174676873</v>
       </c>
       <c r="N12" t="n">
-        <v>147.7716392699215</v>
+        <v>152.2786617681897</v>
       </c>
       <c r="O12" t="n">
-        <v>12.15613586917823</v>
+        <v>12.34012405805508</v>
       </c>
       <c r="P12" t="n">
-        <v>346.1759760471808</v>
+        <v>345.7404129119759</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23303,28 +23509,28 @@
         <v>0.036</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3226995983373241</v>
+        <v>-0.2807925614954142</v>
       </c>
       <c r="J13" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K13" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03895308275933629</v>
+        <v>0.02935477813348009</v>
       </c>
       <c r="M13" t="n">
-        <v>9.785386531800357</v>
+        <v>9.938325858838352</v>
       </c>
       <c r="N13" t="n">
-        <v>155.2208052256273</v>
+        <v>159.1503087347202</v>
       </c>
       <c r="O13" t="n">
-        <v>12.45876419335511</v>
+        <v>12.61547893402071</v>
       </c>
       <c r="P13" t="n">
-        <v>344.927728623639</v>
+        <v>344.5120490077702</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23381,28 +23587,28 @@
         <v>0.0414</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3459053532155055</v>
+        <v>-0.309816698902268</v>
       </c>
       <c r="J14" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K14" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04032651146342381</v>
+        <v>0.03250851965806301</v>
       </c>
       <c r="M14" t="n">
-        <v>10.55113215812219</v>
+        <v>10.63704925864408</v>
       </c>
       <c r="N14" t="n">
-        <v>172.0274436563664</v>
+        <v>174.3870253695629</v>
       </c>
       <c r="O14" t="n">
-        <v>13.11592328646239</v>
+        <v>13.20556796845796</v>
       </c>
       <c r="P14" t="n">
-        <v>339.3172150491116</v>
+        <v>338.9592191495425</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23459,28 +23665,28 @@
         <v>0.042</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3696238851215012</v>
+        <v>-0.3346987687197234</v>
       </c>
       <c r="J15" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K15" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03879526644643283</v>
+        <v>0.03206456638912292</v>
       </c>
       <c r="M15" t="n">
-        <v>11.67792470105582</v>
+        <v>11.7105775494981</v>
       </c>
       <c r="N15" t="n">
-        <v>205.1959883296413</v>
+        <v>207.0769932808031</v>
       </c>
       <c r="O15" t="n">
-        <v>14.32466363757423</v>
+        <v>14.39017002265099</v>
       </c>
       <c r="P15" t="n">
-        <v>336.6832955858426</v>
+        <v>336.3356330765282</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23537,28 +23743,28 @@
         <v>0.0418</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3715480789077861</v>
+        <v>-0.3318566171133502</v>
       </c>
       <c r="J16" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K16" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03474060012477898</v>
+        <v>0.02787099070821708</v>
       </c>
       <c r="M16" t="n">
-        <v>12.59343192806715</v>
+        <v>12.64418558148904</v>
       </c>
       <c r="N16" t="n">
-        <v>233.3952165342882</v>
+        <v>236.0917420887939</v>
       </c>
       <c r="O16" t="n">
-        <v>15.27727778546585</v>
+        <v>15.36527715626353</v>
       </c>
       <c r="P16" t="n">
-        <v>332.625453674029</v>
+        <v>332.2308160378922</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23615,28 +23821,28 @@
         <v>0.0382</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4903767442948465</v>
+        <v>-0.4629464809762934</v>
       </c>
       <c r="J17" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K17" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1087366213052365</v>
+        <v>0.09811147172997503</v>
       </c>
       <c r="M17" t="n">
-        <v>8.485072921906593</v>
+        <v>8.524540498074607</v>
       </c>
       <c r="N17" t="n">
-        <v>118.9973881203273</v>
+        <v>120.1720253771229</v>
       </c>
       <c r="O17" t="n">
-        <v>10.90859239867029</v>
+        <v>10.96230018641722</v>
       </c>
       <c r="P17" t="n">
-        <v>341.1608945834615</v>
+        <v>340.8873932595569</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23693,28 +23899,28 @@
         <v>0.0385</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7806914862043306</v>
+        <v>-0.7523283903024927</v>
       </c>
       <c r="J18" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K18" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1762642359281051</v>
+        <v>0.1665591732623047</v>
       </c>
       <c r="M18" t="n">
-        <v>9.582841823456977</v>
+        <v>9.636426671540759</v>
       </c>
       <c r="N18" t="n">
-        <v>167.8969336879563</v>
+        <v>168.7033854600098</v>
       </c>
       <c r="O18" t="n">
-        <v>12.95750491753549</v>
+        <v>12.98858673836418</v>
       </c>
       <c r="P18" t="n">
-        <v>341.8684835518148</v>
+        <v>341.5806426894617</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -23771,28 +23977,28 @@
         <v>0.0322</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7351673893351058</v>
+        <v>-0.6948125738714708</v>
       </c>
       <c r="J19" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K19" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1310484280178374</v>
+        <v>0.1184458843113624</v>
       </c>
       <c r="M19" t="n">
-        <v>11.14130474787893</v>
+        <v>11.27669998562931</v>
       </c>
       <c r="N19" t="n">
-        <v>213.1356426349748</v>
+        <v>215.9300486031167</v>
       </c>
       <c r="O19" t="n">
-        <v>14.59916581983282</v>
+        <v>14.69455846914485</v>
       </c>
       <c r="P19" t="n">
-        <v>340.6352219063874</v>
+        <v>340.2288130421891</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -23849,28 +24055,28 @@
         <v>0.0311</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7006149140939604</v>
+        <v>-0.6735082999555325</v>
       </c>
       <c r="J20" t="n">
+        <v>213</v>
+      </c>
+      <c r="K20" t="n">
         <v>211</v>
       </c>
-      <c r="K20" t="n">
-        <v>209</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1369889231263259</v>
+        <v>0.1288143399690684</v>
       </c>
       <c r="M20" t="n">
-        <v>10.84650968730926</v>
+        <v>10.89629774859381</v>
       </c>
       <c r="N20" t="n">
-        <v>186.211971619486</v>
+        <v>186.6761470765977</v>
       </c>
       <c r="O20" t="n">
-        <v>13.64595074076871</v>
+        <v>13.66294796435226</v>
       </c>
       <c r="P20" t="n">
-        <v>345.023932715189</v>
+        <v>344.7542027159246</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -23927,28 +24133,28 @@
         <v>0.0339</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5928443192402878</v>
+        <v>-0.5685104923424932</v>
       </c>
       <c r="J21" t="n">
+        <v>213</v>
+      </c>
+      <c r="K21" t="n">
         <v>211</v>
       </c>
-      <c r="K21" t="n">
-        <v>209</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.1275959535559601</v>
+        <v>0.1192437168321709</v>
       </c>
       <c r="M21" t="n">
-        <v>9.62866116406413</v>
+        <v>9.682101556349963</v>
       </c>
       <c r="N21" t="n">
-        <v>145.9213885814862</v>
+        <v>146.4773544441657</v>
       </c>
       <c r="O21" t="n">
-        <v>12.07979257195612</v>
+        <v>12.10278292146751</v>
       </c>
       <c r="P21" t="n">
-        <v>343.7232105985029</v>
+        <v>343.4825335437172</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24005,28 +24211,28 @@
         <v>0.038</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6898084615231764</v>
+        <v>-0.6685469041609772</v>
       </c>
       <c r="J22" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K22" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1617587595907578</v>
+        <v>0.1545843510765177</v>
       </c>
       <c r="M22" t="n">
-        <v>9.599376758765898</v>
+        <v>9.622474606349208</v>
       </c>
       <c r="N22" t="n">
-        <v>149.2295869464966</v>
+        <v>149.4927074783117</v>
       </c>
       <c r="O22" t="n">
-        <v>12.21595624363875</v>
+        <v>12.22672104361229</v>
       </c>
       <c r="P22" t="n">
-        <v>344.3446705103065</v>
+        <v>344.1341839100789</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24083,28 +24289,28 @@
         <v>0.052</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7957829097248427</v>
+        <v>-0.774982567614466</v>
       </c>
       <c r="J23" t="n">
+        <v>213</v>
+      </c>
+      <c r="K23" t="n">
         <v>211</v>
       </c>
-      <c r="K23" t="n">
-        <v>209</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1969839341786889</v>
+        <v>0.1902270270166631</v>
       </c>
       <c r="M23" t="n">
-        <v>9.970683377788221</v>
+        <v>9.992569861585615</v>
       </c>
       <c r="N23" t="n">
-        <v>156.9249022697199</v>
+        <v>157.0386380178251</v>
       </c>
       <c r="O23" t="n">
-        <v>12.52696700202087</v>
+        <v>12.53150581605519</v>
       </c>
       <c r="P23" t="n">
-        <v>340.5942211853903</v>
+        <v>340.3886757280065</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24161,28 +24367,28 @@
         <v>0.0404</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4336314419746095</v>
+        <v>-0.4081926385112856</v>
       </c>
       <c r="J24" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K24" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06679111664642234</v>
+        <v>0.06006215107241675</v>
       </c>
       <c r="M24" t="n">
-        <v>10.01107732586755</v>
+        <v>10.05278167728122</v>
       </c>
       <c r="N24" t="n">
-        <v>159.0004582110158</v>
+        <v>159.4703988499969</v>
       </c>
       <c r="O24" t="n">
-        <v>12.60953838215404</v>
+        <v>12.62815896518558</v>
       </c>
       <c r="P24" t="n">
-        <v>340.8752201597363</v>
+        <v>340.6234867843506</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24239,28 +24445,28 @@
         <v>0.0364</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1969551005154991</v>
+        <v>-0.1964492557151916</v>
       </c>
       <c r="J25" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K25" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02801693403909333</v>
+        <v>0.02842383128437465</v>
       </c>
       <c r="M25" t="n">
-        <v>6.869294813735237</v>
+        <v>6.806658647500518</v>
       </c>
       <c r="N25" t="n">
-        <v>82.13591711510473</v>
+        <v>81.3554911272894</v>
       </c>
       <c r="O25" t="n">
-        <v>9.062886798096109</v>
+        <v>9.01972788543476</v>
       </c>
       <c r="P25" t="n">
-        <v>355.8137072607071</v>
+        <v>355.8087198393727</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24317,28 +24523,28 @@
         <v>0.0501</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4585775586157871</v>
+        <v>-0.428122685420282</v>
       </c>
       <c r="J26" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K26" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1308750083165576</v>
+        <v>0.1146422491076797</v>
       </c>
       <c r="M26" t="n">
-        <v>7.410457452111666</v>
+        <v>7.499688737523816</v>
       </c>
       <c r="N26" t="n">
-        <v>84.5177249415226</v>
+        <v>86.5689332414791</v>
       </c>
       <c r="O26" t="n">
-        <v>9.193352214590856</v>
+        <v>9.304242754866141</v>
       </c>
       <c r="P26" t="n">
-        <v>339.4957396062177</v>
+        <v>339.1943527905304</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24395,28 +24601,28 @@
         <v>0.031</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9371212374814949</v>
+        <v>-0.8601823765703365</v>
       </c>
       <c r="J27" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K27" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1488880303594421</v>
+        <v>0.1243317488345285</v>
       </c>
       <c r="M27" t="n">
-        <v>12.86942256814257</v>
+        <v>13.0158916875917</v>
       </c>
       <c r="N27" t="n">
-        <v>302.8145541006371</v>
+        <v>317.6781649955882</v>
       </c>
       <c r="O27" t="n">
-        <v>17.40156757595813</v>
+        <v>17.82352841037903</v>
       </c>
       <c r="P27" t="n">
-        <v>326.1558301478897</v>
+        <v>325.3922326068884</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24473,28 +24679,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4635968077576765</v>
+        <v>-0.4151821321844035</v>
       </c>
       <c r="J28" t="n">
+        <v>213</v>
+      </c>
+      <c r="K28" t="n">
         <v>211</v>
       </c>
-      <c r="K28" t="n">
-        <v>209</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.03410594321844318</v>
+        <v>0.02755630890462568</v>
       </c>
       <c r="M28" t="n">
-        <v>14.38598657268025</v>
+        <v>14.46779041653483</v>
       </c>
       <c r="N28" t="n">
-        <v>365.1595587799602</v>
+        <v>368.7903624532509</v>
       </c>
       <c r="O28" t="n">
-        <v>19.10914856240225</v>
+        <v>19.20391528968119</v>
       </c>
       <c r="P28" t="n">
-        <v>332.3503988709059</v>
+        <v>331.8674361601054</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24532,7 +24738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC212"/>
+  <dimension ref="A1:AC214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55503,6 +55709,300 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>-35.26815577424759,173.13696264332066</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>-35.26746178122844,173.13657765657643</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>-35.26684558395517,173.13607937039762</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-35.26622729931489,173.1355841182718</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-35.26563430719717,173.13505202724636</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-35.26506243956624,173.13448916724252</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-35.26452576221257,173.13387505437635</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-35.26396210642429,173.13330022418882</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-35.263416217283,173.132699514895</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-35.2627859867249,173.13222162558483</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-35.2622403792912,173.13162049474312</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-35.261679139184245,173.13104212391573</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-35.261050518714505,173.1305618728471</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>-35.26044927368696,173.1300417494541</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>-35.25988252341807,173.12947138606972</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>-35.25931229631128,173.1289060802904</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>-35.25870565719038,173.12839379524445</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>-35.25819770400262,173.12773778924907</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>-35.257617162262896,173.1271874875573</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>-35.257040031803676,173.12663221237736</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>-35.25644507002369,173.1261028991318</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>-35.25584414282218,173.12558226758597</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>-35.25538079549727,173.1248612737895</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>-35.25486153042447,173.12422170664175</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>-35.25425451417495,173.1237099257734</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>-35.25371000512164,173.1231071100242</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>-35.25314210847142,173.1225383479449</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>-35.268241040686796,173.1368384696666</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>-35.267500159744145,173.136521766208</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>-35.26687718968372,173.13603334327127</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-35.26627245019512,173.13551836555806</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-35.2656854201079,173.1349775921298</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-35.26510018076662,173.1344342051856</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-35.264543706564,173.13384892219702</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-35.26396031199674,173.13330283739631</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-35.263414885939795,173.13270145371996</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-35.26284751770202,173.1321320185664</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-35.262228744600684,173.1316374382379</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-35.26165986388576,173.13107019437552</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-35.26105242887264,173.13055909110398</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-35.26048255661191,173.1299932798953</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>-35.25990880234539,173.12943311634172</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>-35.25933255531051,173.12887657731366</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>-35.25873552463224,173.12835029963122</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>-35.25819839859074,173.12773677772597</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>-35.25763093820236,173.12716742576242</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>-35.25708367471287,173.12656865549855</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>-35.256510418359845,173.12600773280414</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>-35.25590729142208,173.125490304808</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>-35.25539132985073,173.12484593264074</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>-35.25486529267431,173.12421622767508</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>-35.25427737699078,173.1236766306669</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>-35.25369935514839,173.12312261958618</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>-35.253172495480904,173.12249409526677</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
